--- a/artfynd/A 19278-2025 artfynd.xlsx
+++ b/artfynd/A 19278-2025 artfynd.xlsx
@@ -1971,7 +1971,7 @@
         <v>127079637</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>127081113</v>
       </c>
       <c r="B14" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2166,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127080401</v>
+        <v>127080248</v>
       </c>
       <c r="B15" t="n">
-        <v>80083</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,34 +2177,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592166</v>
+        <v>592154</v>
       </c>
       <c r="R15" t="n">
-        <v>6985095</v>
+        <v>6985108</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2237,6 +2242,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2263,10 +2273,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127080248</v>
+        <v>127080401</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>80114</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2274,39 +2284,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>592154</v>
+        <v>592166</v>
       </c>
       <c r="R16" t="n">
-        <v>6985108</v>
+        <v>6985095</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2339,11 +2344,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2373,7 +2373,7 @@
         <v>127080985</v>
       </c>
       <c r="B17" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>127079693</v>
       </c>
       <c r="B18" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>127080303</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2977,10 +2977,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127103015</v>
+        <v>127103018</v>
       </c>
       <c r="B23" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3012,10 +3012,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>592352</v>
+        <v>592280</v>
       </c>
       <c r="R23" t="n">
-        <v>6985245</v>
+        <v>6985186</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3074,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127103018</v>
+        <v>127103015</v>
       </c>
       <c r="B24" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3109,10 +3109,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592280</v>
+        <v>592352</v>
       </c>
       <c r="R24" t="n">
-        <v>6985186</v>
+        <v>6985245</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3174,7 +3174,7 @@
         <v>127103016</v>
       </c>
       <c r="B25" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>127102994</v>
       </c>
       <c r="B26" t="n">
-        <v>80111</v>
+        <v>80142</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3365,10 +3365,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127102982</v>
+        <v>127102993</v>
       </c>
       <c r="B27" t="n">
-        <v>79987</v>
+        <v>80142</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3376,21 +3376,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>6461</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592287</v>
+        <v>592331</v>
       </c>
       <c r="R27" t="n">
-        <v>6985142</v>
+        <v>6985243</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3462,10 +3462,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127102993</v>
+        <v>127102982</v>
       </c>
       <c r="B28" t="n">
-        <v>80111</v>
+        <v>80018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3473,21 +3473,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6461</v>
+        <v>6456</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3497,10 +3497,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>592331</v>
+        <v>592287</v>
       </c>
       <c r="R28" t="n">
-        <v>6985243</v>
+        <v>6985142</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3562,7 +3562,7 @@
         <v>127103014</v>
       </c>
       <c r="B29" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>127103017</v>
       </c>
       <c r="B30" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>127103034</v>
       </c>
       <c r="B31" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>127150246</v>
       </c>
       <c r="B34" t="n">
-        <v>79987</v>
+        <v>80018</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 19278-2025 artfynd.xlsx
+++ b/artfynd/A 19278-2025 artfynd.xlsx
@@ -1971,7 +1971,7 @@
         <v>127079637</v>
       </c>
       <c r="B13" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>127081113</v>
       </c>
       <c r="B14" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2166,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127080248</v>
+        <v>127080401</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>80117</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,39 +2177,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592154</v>
+        <v>592166</v>
       </c>
       <c r="R15" t="n">
-        <v>6985108</v>
+        <v>6985095</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2242,11 +2237,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2273,10 +2263,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127080401</v>
+        <v>127080248</v>
       </c>
       <c r="B16" t="n">
-        <v>80114</v>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,34 +2274,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>592166</v>
+        <v>592154</v>
       </c>
       <c r="R16" t="n">
-        <v>6985095</v>
+        <v>6985108</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2344,6 +2339,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2373,7 +2373,7 @@
         <v>127080985</v>
       </c>
       <c r="B17" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>127079693</v>
       </c>
       <c r="B18" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>127080303</v>
       </c>
       <c r="B21" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2977,10 +2977,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127103018</v>
+        <v>127103015</v>
       </c>
       <c r="B23" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3012,10 +3012,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>592280</v>
+        <v>592352</v>
       </c>
       <c r="R23" t="n">
-        <v>6985186</v>
+        <v>6985245</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3074,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127103015</v>
+        <v>127103018</v>
       </c>
       <c r="B24" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3109,10 +3109,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592352</v>
+        <v>592280</v>
       </c>
       <c r="R24" t="n">
-        <v>6985245</v>
+        <v>6985186</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3174,7 +3174,7 @@
         <v>127103016</v>
       </c>
       <c r="B25" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>127102994</v>
       </c>
       <c r="B26" t="n">
-        <v>80142</v>
+        <v>80145</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>127102993</v>
       </c>
       <c r="B27" t="n">
-        <v>80142</v>
+        <v>80145</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>127102982</v>
       </c>
       <c r="B28" t="n">
-        <v>80018</v>
+        <v>80021</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>127103014</v>
       </c>
       <c r="B29" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3656,10 +3656,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127103017</v>
+        <v>127103034</v>
       </c>
       <c r="B30" t="n">
-        <v>80114</v>
+        <v>79014</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3667,21 +3667,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592296</v>
+        <v>592283</v>
       </c>
       <c r="R30" t="n">
-        <v>6985199</v>
+        <v>6985161</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3753,10 +3753,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127103034</v>
+        <v>127103017</v>
       </c>
       <c r="B31" t="n">
-        <v>79011</v>
+        <v>80117</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3764,21 +3764,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>592283</v>
+        <v>592296</v>
       </c>
       <c r="R31" t="n">
-        <v>6985161</v>
+        <v>6985199</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3850,7 +3850,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127081549</v>
+        <v>127081843</v>
       </c>
       <c r="B32" t="n">
         <v>57657</v>
@@ -3883,11 +3883,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M32" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -3899,10 +3894,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>592259</v>
+        <v>592283</v>
       </c>
       <c r="R32" t="n">
-        <v>6985113</v>
+        <v>6985149</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3961,7 +3956,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127081843</v>
+        <v>127081549</v>
       </c>
       <c r="B33" t="n">
         <v>57657</v>
@@ -3994,6 +3989,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>592283</v>
+        <v>592259</v>
       </c>
       <c r="R33" t="n">
-        <v>6985149</v>
+        <v>6985113</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4070,7 +4070,7 @@
         <v>127150246</v>
       </c>
       <c r="B34" t="n">
-        <v>80018</v>
+        <v>80021</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 19278-2025 artfynd.xlsx
+++ b/artfynd/A 19278-2025 artfynd.xlsx
@@ -2977,7 +2977,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127103015</v>
+        <v>127103018</v>
       </c>
       <c r="B23" t="n">
         <v>80117</v>
@@ -3012,10 +3012,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>592352</v>
+        <v>592280</v>
       </c>
       <c r="R23" t="n">
-        <v>6985245</v>
+        <v>6985186</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3074,7 +3074,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127103018</v>
+        <v>127103015</v>
       </c>
       <c r="B24" t="n">
         <v>80117</v>
@@ -3109,10 +3109,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592280</v>
+        <v>592352</v>
       </c>
       <c r="R24" t="n">
-        <v>6985186</v>
+        <v>6985245</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3656,10 +3656,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127103034</v>
+        <v>127103017</v>
       </c>
       <c r="B30" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3667,21 +3667,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592283</v>
+        <v>592296</v>
       </c>
       <c r="R30" t="n">
-        <v>6985161</v>
+        <v>6985199</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3753,10 +3753,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127103017</v>
+        <v>127103034</v>
       </c>
       <c r="B31" t="n">
-        <v>80117</v>
+        <v>79014</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3764,21 +3764,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>592296</v>
+        <v>592283</v>
       </c>
       <c r="R31" t="n">
-        <v>6985199</v>
+        <v>6985161</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 19278-2025 artfynd.xlsx
+++ b/artfynd/A 19278-2025 artfynd.xlsx
@@ -1968,45 +1968,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127079637</v>
+        <v>127081113</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592052</v>
+        <v>592190</v>
       </c>
       <c r="R13" t="n">
-        <v>6985096</v>
+        <v>6985106</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2065,49 +2069,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127081113</v>
+        <v>127079637</v>
       </c>
       <c r="B14" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592190</v>
+        <v>592052</v>
       </c>
       <c r="R14" t="n">
-        <v>6985106</v>
+        <v>6985096</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 19278-2025 artfynd.xlsx
+++ b/artfynd/A 19278-2025 artfynd.xlsx
@@ -1968,49 +1968,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127081113</v>
+        <v>127079637</v>
       </c>
       <c r="B13" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592190</v>
+        <v>592052</v>
       </c>
       <c r="R13" t="n">
-        <v>6985106</v>
+        <v>6985096</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2069,45 +2065,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127079637</v>
+        <v>127081113</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592052</v>
+        <v>592190</v>
       </c>
       <c r="R14" t="n">
-        <v>6985096</v>
+        <v>6985106</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2373,7 +2373,7 @@
         <v>127080985</v>
       </c>
       <c r="B17" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 19278-2025 artfynd.xlsx
+++ b/artfynd/A 19278-2025 artfynd.xlsx
@@ -1968,45 +1968,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127079637</v>
+        <v>127081113</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592052</v>
+        <v>592190</v>
       </c>
       <c r="R13" t="n">
-        <v>6985096</v>
+        <v>6985106</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2065,49 +2069,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127081113</v>
+        <v>127079637</v>
       </c>
       <c r="B14" t="n">
-        <v>98443</v>
+        <v>79014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592190</v>
+        <v>592052</v>
       </c>
       <c r="R14" t="n">
-        <v>6985106</v>
+        <v>6985096</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -3850,7 +3850,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127081843</v>
+        <v>127081549</v>
       </c>
       <c r="B32" t="n">
         <v>57657</v>
@@ -3883,6 +3883,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -3894,10 +3899,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>592283</v>
+        <v>592259</v>
       </c>
       <c r="R32" t="n">
-        <v>6985149</v>
+        <v>6985113</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3956,7 +3961,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127081549</v>
+        <v>127081843</v>
       </c>
       <c r="B33" t="n">
         <v>57657</v>
@@ -3989,11 +3994,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M33" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>592259</v>
+        <v>592283</v>
       </c>
       <c r="R33" t="n">
-        <v>6985113</v>
+        <v>6985149</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 19278-2025 artfynd.xlsx
+++ b/artfynd/A 19278-2025 artfynd.xlsx
@@ -1971,7 +1971,7 @@
         <v>127081113</v>
       </c>
       <c r="B13" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
         <v>127079637</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>127080401</v>
       </c>
       <c r="B15" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>127080248</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>127080985</v>
       </c>
       <c r="B17" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>127079693</v>
       </c>
       <c r="B18" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>127081614</v>
       </c>
       <c r="B19" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>127080122</v>
       </c>
       <c r="B20" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>127080303</v>
       </c>
       <c r="B21" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>127086951</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>127103018</v>
       </c>
       <c r="B23" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>127103015</v>
       </c>
       <c r="B24" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>127103016</v>
       </c>
       <c r="B25" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>127102994</v>
       </c>
       <c r="B26" t="n">
-        <v>80145</v>
+        <v>80149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>127102993</v>
       </c>
       <c r="B27" t="n">
-        <v>80145</v>
+        <v>80149</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>127102982</v>
       </c>
       <c r="B28" t="n">
-        <v>80021</v>
+        <v>80025</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>127103014</v>
       </c>
       <c r="B29" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>127103017</v>
       </c>
       <c r="B30" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>127103034</v>
       </c>
       <c r="B31" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>127081549</v>
       </c>
       <c r="B32" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3964,7 +3964,7 @@
         <v>127081843</v>
       </c>
       <c r="B33" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>127150246</v>
       </c>
       <c r="B34" t="n">
-        <v>80021</v>
+        <v>80025</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 19278-2025 artfynd.xlsx
+++ b/artfynd/A 19278-2025 artfynd.xlsx
@@ -1968,49 +1968,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127081113</v>
+        <v>127079637</v>
       </c>
       <c r="B13" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592190</v>
+        <v>592052</v>
       </c>
       <c r="R13" t="n">
-        <v>6985106</v>
+        <v>6985096</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2069,45 +2065,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127079637</v>
+        <v>127081113</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592052</v>
+        <v>592190</v>
       </c>
       <c r="R14" t="n">
-        <v>6985096</v>
+        <v>6985106</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -3850,7 +3850,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127081549</v>
+        <v>127081843</v>
       </c>
       <c r="B32" t="n">
         <v>57661</v>
@@ -3883,11 +3883,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M32" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -3899,10 +3894,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>592259</v>
+        <v>592283</v>
       </c>
       <c r="R32" t="n">
-        <v>6985113</v>
+        <v>6985149</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3961,7 +3956,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127081843</v>
+        <v>127081549</v>
       </c>
       <c r="B33" t="n">
         <v>57661</v>
@@ -3994,6 +3989,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>592283</v>
+        <v>592259</v>
       </c>
       <c r="R33" t="n">
-        <v>6985149</v>
+        <v>6985113</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>

--- a/artfynd/A 19278-2025 artfynd.xlsx
+++ b/artfynd/A 19278-2025 artfynd.xlsx
@@ -2068,7 +2068,7 @@
         <v>127081113</v>
       </c>
       <c r="B14" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2166,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127080401</v>
+        <v>127080248</v>
       </c>
       <c r="B15" t="n">
-        <v>80121</v>
+        <v>57661</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,34 +2177,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592166</v>
+        <v>592154</v>
       </c>
       <c r="R15" t="n">
-        <v>6985095</v>
+        <v>6985108</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2237,6 +2242,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2263,10 +2273,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127080248</v>
+        <v>127080401</v>
       </c>
       <c r="B16" t="n">
-        <v>57661</v>
+        <v>80121</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2274,39 +2284,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>592154</v>
+        <v>592166</v>
       </c>
       <c r="R16" t="n">
-        <v>6985108</v>
+        <v>6985095</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2339,11 +2344,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2977,7 +2977,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127103018</v>
+        <v>127103015</v>
       </c>
       <c r="B23" t="n">
         <v>80121</v>
@@ -3012,10 +3012,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>592280</v>
+        <v>592352</v>
       </c>
       <c r="R23" t="n">
-        <v>6985186</v>
+        <v>6985245</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3074,7 +3074,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127103015</v>
+        <v>127103018</v>
       </c>
       <c r="B24" t="n">
         <v>80121</v>
@@ -3109,10 +3109,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592352</v>
+        <v>592280</v>
       </c>
       <c r="R24" t="n">
-        <v>6985245</v>
+        <v>6985186</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3365,10 +3365,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127102993</v>
+        <v>127102982</v>
       </c>
       <c r="B27" t="n">
-        <v>80149</v>
+        <v>80025</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3376,21 +3376,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6461</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592331</v>
+        <v>592287</v>
       </c>
       <c r="R27" t="n">
-        <v>6985243</v>
+        <v>6985142</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3462,10 +3462,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127102982</v>
+        <v>127102993</v>
       </c>
       <c r="B28" t="n">
-        <v>80025</v>
+        <v>80149</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3473,21 +3473,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6456</v>
+        <v>6461</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3497,10 +3497,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>592287</v>
+        <v>592331</v>
       </c>
       <c r="R28" t="n">
-        <v>6985142</v>
+        <v>6985243</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 19278-2025 artfynd.xlsx
+++ b/artfynd/A 19278-2025 artfynd.xlsx
@@ -1971,7 +1971,7 @@
         <v>127079637</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>127081113</v>
       </c>
       <c r="B14" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2166,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127080248</v>
+        <v>127080401</v>
       </c>
       <c r="B15" t="n">
-        <v>57661</v>
+        <v>80123</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,39 +2177,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592154</v>
+        <v>592166</v>
       </c>
       <c r="R15" t="n">
-        <v>6985108</v>
+        <v>6985095</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2242,11 +2237,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2273,10 +2263,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127080401</v>
+        <v>127080248</v>
       </c>
       <c r="B16" t="n">
-        <v>80121</v>
+        <v>57663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,34 +2274,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>592166</v>
+        <v>592154</v>
       </c>
       <c r="R16" t="n">
-        <v>6985095</v>
+        <v>6985108</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2344,6 +2339,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2373,7 +2373,7 @@
         <v>127080985</v>
       </c>
       <c r="B17" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>127079693</v>
       </c>
       <c r="B18" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>127081614</v>
       </c>
       <c r="B19" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>127080122</v>
       </c>
       <c r="B20" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>127080303</v>
       </c>
       <c r="B21" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>127086951</v>
       </c>
       <c r="B22" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2977,10 +2977,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127103015</v>
+        <v>127103018</v>
       </c>
       <c r="B23" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3012,10 +3012,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>592352</v>
+        <v>592280</v>
       </c>
       <c r="R23" t="n">
-        <v>6985245</v>
+        <v>6985186</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3074,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127103018</v>
+        <v>127103015</v>
       </c>
       <c r="B24" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3109,10 +3109,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592280</v>
+        <v>592352</v>
       </c>
       <c r="R24" t="n">
-        <v>6985186</v>
+        <v>6985245</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3174,7 +3174,7 @@
         <v>127103016</v>
       </c>
       <c r="B25" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>127102994</v>
       </c>
       <c r="B26" t="n">
-        <v>80149</v>
+        <v>80151</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3365,10 +3365,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127102982</v>
+        <v>127102993</v>
       </c>
       <c r="B27" t="n">
-        <v>80025</v>
+        <v>80151</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3376,21 +3376,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>6461</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592287</v>
+        <v>592331</v>
       </c>
       <c r="R27" t="n">
-        <v>6985142</v>
+        <v>6985243</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3462,10 +3462,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127102993</v>
+        <v>127102982</v>
       </c>
       <c r="B28" t="n">
-        <v>80149</v>
+        <v>80027</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3473,21 +3473,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6461</v>
+        <v>6456</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3497,10 +3497,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>592331</v>
+        <v>592287</v>
       </c>
       <c r="R28" t="n">
-        <v>6985243</v>
+        <v>6985142</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3562,7 +3562,7 @@
         <v>127103014</v>
       </c>
       <c r="B29" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>127103017</v>
       </c>
       <c r="B30" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>127103034</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>127081843</v>
       </c>
       <c r="B32" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3959,7 +3959,7 @@
         <v>127081549</v>
       </c>
       <c r="B33" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>127150246</v>
       </c>
       <c r="B34" t="n">
-        <v>80025</v>
+        <v>80027</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 19278-2025 artfynd.xlsx
+++ b/artfynd/A 19278-2025 artfynd.xlsx
@@ -3656,10 +3656,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127103017</v>
+        <v>127103034</v>
       </c>
       <c r="B30" t="n">
-        <v>80123</v>
+        <v>79020</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3667,21 +3667,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592296</v>
+        <v>592283</v>
       </c>
       <c r="R30" t="n">
-        <v>6985199</v>
+        <v>6985161</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3753,10 +3753,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127103034</v>
+        <v>127103017</v>
       </c>
       <c r="B31" t="n">
-        <v>79020</v>
+        <v>80123</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3764,21 +3764,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>592283</v>
+        <v>592296</v>
       </c>
       <c r="R31" t="n">
-        <v>6985161</v>
+        <v>6985199</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 19278-2025 artfynd.xlsx
+++ b/artfynd/A 19278-2025 artfynd.xlsx
@@ -1968,45 +1968,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127079637</v>
+        <v>127081113</v>
       </c>
       <c r="B13" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592052</v>
+        <v>592190</v>
       </c>
       <c r="R13" t="n">
-        <v>6985096</v>
+        <v>6985106</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2065,49 +2069,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127081113</v>
+        <v>127079637</v>
       </c>
       <c r="B14" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592190</v>
+        <v>592052</v>
       </c>
       <c r="R14" t="n">
-        <v>6985106</v>
+        <v>6985096</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 19278-2025 artfynd.xlsx
+++ b/artfynd/A 19278-2025 artfynd.xlsx
@@ -1968,49 +1968,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127081113</v>
+        <v>127079637</v>
       </c>
       <c r="B13" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592190</v>
+        <v>592052</v>
       </c>
       <c r="R13" t="n">
-        <v>6985106</v>
+        <v>6985096</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2069,45 +2065,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127079637</v>
+        <v>127081113</v>
       </c>
       <c r="B14" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592052</v>
+        <v>592190</v>
       </c>
       <c r="R14" t="n">
-        <v>6985096</v>
+        <v>6985106</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -3656,10 +3656,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127103034</v>
+        <v>127103017</v>
       </c>
       <c r="B30" t="n">
-        <v>79020</v>
+        <v>80123</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3667,21 +3667,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592283</v>
+        <v>592296</v>
       </c>
       <c r="R30" t="n">
-        <v>6985161</v>
+        <v>6985199</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3753,10 +3753,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127103017</v>
+        <v>127103034</v>
       </c>
       <c r="B31" t="n">
-        <v>80123</v>
+        <v>79020</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3764,21 +3764,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3788,10 +3788,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>592296</v>
+        <v>592283</v>
       </c>
       <c r="R31" t="n">
-        <v>6985199</v>
+        <v>6985161</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 19278-2025 artfynd.xlsx
+++ b/artfynd/A 19278-2025 artfynd.xlsx
@@ -2068,7 +2068,7 @@
         <v>127081113</v>
       </c>
       <c r="B14" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2166,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127080401</v>
+        <v>127080248</v>
       </c>
       <c r="B15" t="n">
-        <v>80123</v>
+        <v>57663</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,34 +2177,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592166</v>
+        <v>592154</v>
       </c>
       <c r="R15" t="n">
-        <v>6985095</v>
+        <v>6985108</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2237,6 +2242,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2263,10 +2273,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127080248</v>
+        <v>127080401</v>
       </c>
       <c r="B16" t="n">
-        <v>57663</v>
+        <v>80123</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2274,39 +2284,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>592154</v>
+        <v>592166</v>
       </c>
       <c r="R16" t="n">
-        <v>6985108</v>
+        <v>6985095</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2339,11 +2344,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2373,7 +2373,7 @@
         <v>127080985</v>
       </c>
       <c r="B17" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 19278-2025 artfynd.xlsx
+++ b/artfynd/A 19278-2025 artfynd.xlsx
@@ -1971,7 +1971,7 @@
         <v>127079637</v>
       </c>
       <c r="B13" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>127081113</v>
       </c>
       <c r="B14" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2166,10 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127080248</v>
+        <v>127080401</v>
       </c>
       <c r="B15" t="n">
-        <v>57663</v>
+        <v>80126</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2177,39 +2177,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592154</v>
+        <v>592166</v>
       </c>
       <c r="R15" t="n">
-        <v>6985108</v>
+        <v>6985095</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2242,11 +2237,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2273,10 +2263,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127080401</v>
+        <v>127080248</v>
       </c>
       <c r="B16" t="n">
-        <v>80123</v>
+        <v>57666</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2284,34 +2274,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Svartabborrtjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>592166</v>
+        <v>592154</v>
       </c>
       <c r="R16" t="n">
-        <v>6985095</v>
+        <v>6985108</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2344,6 +2339,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2373,7 +2373,7 @@
         <v>127080985</v>
       </c>
       <c r="B17" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>127079693</v>
       </c>
       <c r="B18" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>127081614</v>
       </c>
       <c r="B19" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>127080122</v>
       </c>
       <c r="B20" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>127080303</v>
       </c>
       <c r="B21" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>127086951</v>
       </c>
       <c r="B22" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>127103018</v>
       </c>
       <c r="B23" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>127103015</v>
       </c>
       <c r="B24" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>127103016</v>
       </c>
       <c r="B25" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>127102994</v>
       </c>
       <c r="B26" t="n">
-        <v>80151</v>
+        <v>80154</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>127102993</v>
       </c>
       <c r="B27" t="n">
-        <v>80151</v>
+        <v>80154</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>127102982</v>
       </c>
       <c r="B28" t="n">
-        <v>80027</v>
+        <v>80030</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>127103014</v>
       </c>
       <c r="B29" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>127103017</v>
       </c>
       <c r="B30" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>127103034</v>
       </c>
       <c r="B31" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3850,10 +3850,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127081843</v>
+        <v>127081549</v>
       </c>
       <c r="B32" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3883,6 +3883,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -3894,10 +3899,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>592283</v>
+        <v>592259</v>
       </c>
       <c r="R32" t="n">
-        <v>6985149</v>
+        <v>6985113</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3956,10 +3961,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127081549</v>
+        <v>127081843</v>
       </c>
       <c r="B33" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3989,11 +3994,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M33" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>592259</v>
+        <v>592283</v>
       </c>
       <c r="R33" t="n">
-        <v>6985113</v>
+        <v>6985149</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4070,7 +4070,7 @@
         <v>127150246</v>
       </c>
       <c r="B34" t="n">
-        <v>80027</v>
+        <v>80030</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 19278-2025 artfynd.xlsx
+++ b/artfynd/A 19278-2025 artfynd.xlsx
@@ -2980,7 +2980,7 @@
         <v>127103018</v>
       </c>
       <c r="B23" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
         <v>127103015</v>
       </c>
       <c r="B24" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>127103016</v>
       </c>
       <c r="B25" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>127102994</v>
       </c>
       <c r="B26" t="n">
-        <v>80154</v>
+        <v>80160</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3368,7 +3368,7 @@
         <v>127102993</v>
       </c>
       <c r="B27" t="n">
-        <v>80154</v>
+        <v>80160</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>127102982</v>
       </c>
       <c r="B28" t="n">
-        <v>80030</v>
+        <v>80036</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3562,7 +3562,7 @@
         <v>127103014</v>
       </c>
       <c r="B29" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>127103017</v>
       </c>
       <c r="B30" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>127103034</v>
       </c>
       <c r="B31" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3850,10 +3850,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127081549</v>
+        <v>127081843</v>
       </c>
       <c r="B32" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3883,11 +3883,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M32" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -3899,10 +3894,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>592259</v>
+        <v>592283</v>
       </c>
       <c r="R32" t="n">
-        <v>6985113</v>
+        <v>6985149</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3961,10 +3956,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127081843</v>
+        <v>127081549</v>
       </c>
       <c r="B33" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3994,6 +3989,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
           <t>födosökande</t>
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>592283</v>
+        <v>592259</v>
       </c>
       <c r="R33" t="n">
-        <v>6985149</v>
+        <v>6985113</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4070,7 +4070,7 @@
         <v>127150246</v>
       </c>
       <c r="B34" t="n">
-        <v>80030</v>
+        <v>80036</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 19278-2025 artfynd.xlsx
+++ b/artfynd/A 19278-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3074,10 +3074,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127103015</v>
+        <v>129431324</v>
       </c>
       <c r="B24" t="n">
-        <v>80132</v>
+        <v>80148</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Svartabborrtjärnbäcken, Jmt</t>
+          <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
@@ -3115,7 +3115,7 @@
         <v>6985245</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3139,12 +3139,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3159,12 +3159,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -4166,6 +4166,2077 @@
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129431323</v>
+      </c>
+      <c r="B35" t="n">
+        <v>56908</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>592351</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6985215</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129431306</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>592083</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6985107</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129431285</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>592323</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6985292</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129431327</v>
+      </c>
+      <c r="B38" t="n">
+        <v>80148</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>592131</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6985450</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129431326</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57887</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>592165</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6985420</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129431325</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57831</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>592216</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6985353</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129431330</v>
+      </c>
+      <c r="B41" t="n">
+        <v>56920</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>592177</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6985180</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129431332</v>
+      </c>
+      <c r="B42" t="n">
+        <v>80148</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>592076</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6985249</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129431331</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57724</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>592122</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6985241</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129431288</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>592108</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6985513</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129431286</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>592152</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6985427</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129431289</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>592100</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6985482</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129431290</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>592103</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6985482</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129431291</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>592111</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6985480</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129431343</v>
+      </c>
+      <c r="B49" t="n">
+        <v>80148</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>592025</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6985134</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129431329</v>
+      </c>
+      <c r="B50" t="n">
+        <v>56908</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>592273</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6985252</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129431333</v>
+      </c>
+      <c r="B51" t="n">
+        <v>80148</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>592069</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6985226</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129431287</v>
+      </c>
+      <c r="B52" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>592138</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6985435</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>129431321</v>
+      </c>
+      <c r="B53" t="n">
+        <v>56908</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>592426</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6985175</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129431342</v>
+      </c>
+      <c r="B54" t="n">
+        <v>80148</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>592042</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6985102</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19278-2025 artfynd.xlsx
+++ b/artfynd/A 19278-2025 artfynd.xlsx
@@ -3077,7 +3077,7 @@
         <v>129431324</v>
       </c>
       <c r="B24" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4168,10 +4168,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129431323</v>
+        <v>129431306</v>
       </c>
       <c r="B35" t="n">
-        <v>56908</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4179,16 +4179,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4196,16 +4196,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4215,10 +4211,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>592351</v>
+        <v>592083</v>
       </c>
       <c r="R35" t="n">
-        <v>6985215</v>
+        <v>6985107</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4245,12 +4241,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4277,10 +4273,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129431306</v>
+        <v>129431323</v>
       </c>
       <c r="B36" t="n">
-        <v>57727</v>
+        <v>56908</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4288,16 +4284,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4305,12 +4301,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4320,10 +4320,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>592083</v>
+        <v>592351</v>
       </c>
       <c r="R36" t="n">
-        <v>6985107</v>
+        <v>6985215</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4487,7 +4487,7 @@
         <v>129431327</v>
       </c>
       <c r="B38" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4690,10 +4690,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129431325</v>
+        <v>129431330</v>
       </c>
       <c r="B40" t="n">
-        <v>57831</v>
+        <v>56920</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4701,16 +4701,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103031</v>
+        <v>102613</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4720,11 +4720,15 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -4737,10 +4741,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>592216</v>
+        <v>592177</v>
       </c>
       <c r="R40" t="n">
-        <v>6985353</v>
+        <v>6985180</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4799,10 +4803,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129431330</v>
+        <v>129431325</v>
       </c>
       <c r="B41" t="n">
-        <v>56920</v>
+        <v>57831</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4810,16 +4814,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102613</v>
+        <v>103031</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4829,15 +4833,11 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>592177</v>
+        <v>592216</v>
       </c>
       <c r="R41" t="n">
-        <v>6985180</v>
+        <v>6985353</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4915,7 +4915,7 @@
         <v>129431332</v>
       </c>
       <c r="B42" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>129431343</v>
       </c>
       <c r="B49" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>129431333</v>
       </c>
       <c r="B51" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>129431342</v>
       </c>
       <c r="B54" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 19278-2025 artfynd.xlsx
+++ b/artfynd/A 19278-2025 artfynd.xlsx
@@ -4912,10 +4912,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129431332</v>
+        <v>129431331</v>
       </c>
       <c r="B42" t="n">
-        <v>80149</v>
+        <v>57724</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4923,34 +4923,46 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>592076</v>
+        <v>592122</v>
       </c>
       <c r="R42" t="n">
-        <v>6985249</v>
+        <v>6985241</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5009,10 +5021,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129431331</v>
+        <v>129431288</v>
       </c>
       <c r="B43" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5020,16 +5032,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5037,29 +5049,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>592122</v>
+        <v>592108</v>
       </c>
       <c r="R43" t="n">
-        <v>6985241</v>
+        <v>6985513</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5118,10 +5123,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129431288</v>
+        <v>129431332</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5129,39 +5134,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>592108</v>
+        <v>592076</v>
       </c>
       <c r="R44" t="n">
-        <v>6985513</v>
+        <v>6985249</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>

--- a/artfynd/A 19278-2025 artfynd.xlsx
+++ b/artfynd/A 19278-2025 artfynd.xlsx
@@ -4484,10 +4484,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129431327</v>
+        <v>129431326</v>
       </c>
       <c r="B38" t="n">
-        <v>80149</v>
+        <v>57887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4495,34 +4495,46 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>592131</v>
+        <v>592165</v>
       </c>
       <c r="R38" t="n">
-        <v>6985450</v>
+        <v>6985420</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4581,10 +4593,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129431326</v>
+        <v>129431327</v>
       </c>
       <c r="B39" t="n">
-        <v>57887</v>
+        <v>80149</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4592,46 +4604,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>592165</v>
+        <v>592131</v>
       </c>
       <c r="R39" t="n">
-        <v>6985420</v>
+        <v>6985450</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5931,10 +5931,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129431287</v>
+        <v>129431321</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>56908</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5942,16 +5942,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5959,22 +5959,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>592138</v>
+        <v>592426</v>
       </c>
       <c r="R52" t="n">
-        <v>6985435</v>
+        <v>6985175</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6033,10 +6040,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129431321</v>
+        <v>129431287</v>
       </c>
       <c r="B53" t="n">
-        <v>56908</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6044,16 +6051,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6061,29 +6068,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>592426</v>
+        <v>592138</v>
       </c>
       <c r="R53" t="n">
-        <v>6985175</v>
+        <v>6985435</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>

--- a/artfynd/A 19278-2025 artfynd.xlsx
+++ b/artfynd/A 19278-2025 artfynd.xlsx
@@ -4484,10 +4484,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129431326</v>
+        <v>129431327</v>
       </c>
       <c r="B38" t="n">
-        <v>57887</v>
+        <v>80149</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4495,46 +4495,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>592165</v>
+        <v>592131</v>
       </c>
       <c r="R38" t="n">
-        <v>6985420</v>
+        <v>6985450</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4593,10 +4581,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129431327</v>
+        <v>129431326</v>
       </c>
       <c r="B39" t="n">
-        <v>80149</v>
+        <v>57887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4604,34 +4592,46 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>592131</v>
+        <v>592165</v>
       </c>
       <c r="R39" t="n">
-        <v>6985450</v>
+        <v>6985420</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4690,10 +4690,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129431330</v>
+        <v>129431325</v>
       </c>
       <c r="B40" t="n">
-        <v>56920</v>
+        <v>57831</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4701,16 +4701,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102613</v>
+        <v>103031</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4720,15 +4720,11 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -4741,10 +4737,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>592177</v>
+        <v>592216</v>
       </c>
       <c r="R40" t="n">
-        <v>6985180</v>
+        <v>6985353</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4803,10 +4799,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129431325</v>
+        <v>129431330</v>
       </c>
       <c r="B41" t="n">
-        <v>57831</v>
+        <v>56920</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4814,16 +4810,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103031</v>
+        <v>102613</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4833,11 +4829,15 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>592216</v>
+        <v>592177</v>
       </c>
       <c r="R41" t="n">
-        <v>6985353</v>
+        <v>6985180</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5021,10 +5021,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129431288</v>
+        <v>129431332</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5032,39 +5032,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>592108</v>
+        <v>592076</v>
       </c>
       <c r="R43" t="n">
-        <v>6985513</v>
+        <v>6985249</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5123,10 +5118,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129431332</v>
+        <v>129431288</v>
       </c>
       <c r="B44" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5134,34 +5129,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>592076</v>
+        <v>592108</v>
       </c>
       <c r="R44" t="n">
-        <v>6985249</v>
+        <v>6985513</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5931,10 +5931,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129431321</v>
+        <v>129431287</v>
       </c>
       <c r="B52" t="n">
-        <v>56908</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5942,16 +5942,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5959,29 +5959,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>592426</v>
+        <v>592138</v>
       </c>
       <c r="R52" t="n">
-        <v>6985175</v>
+        <v>6985435</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6040,10 +6033,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129431287</v>
+        <v>129431321</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>56908</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6051,16 +6044,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6068,22 +6061,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>592138</v>
+        <v>592426</v>
       </c>
       <c r="R53" t="n">
-        <v>6985435</v>
+        <v>6985175</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>

--- a/artfynd/A 19278-2025 artfynd.xlsx
+++ b/artfynd/A 19278-2025 artfynd.xlsx
@@ -4690,10 +4690,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129431325</v>
+        <v>129431330</v>
       </c>
       <c r="B40" t="n">
-        <v>57831</v>
+        <v>56920</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4701,16 +4701,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103031</v>
+        <v>102613</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4720,11 +4720,15 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -4737,10 +4741,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>592216</v>
+        <v>592177</v>
       </c>
       <c r="R40" t="n">
-        <v>6985353</v>
+        <v>6985180</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4799,10 +4803,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129431330</v>
+        <v>129431325</v>
       </c>
       <c r="B41" t="n">
-        <v>56920</v>
+        <v>57831</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4810,16 +4814,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102613</v>
+        <v>103031</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4829,15 +4833,11 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>592177</v>
+        <v>592216</v>
       </c>
       <c r="R41" t="n">
-        <v>6985180</v>
+        <v>6985353</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4912,10 +4912,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129431331</v>
+        <v>129431332</v>
       </c>
       <c r="B42" t="n">
-        <v>57724</v>
+        <v>80149</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4923,46 +4923,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>592122</v>
+        <v>592076</v>
       </c>
       <c r="R42" t="n">
-        <v>6985241</v>
+        <v>6985249</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5021,10 +5009,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129431332</v>
+        <v>129431288</v>
       </c>
       <c r="B43" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5032,34 +5020,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>592076</v>
+        <v>592108</v>
       </c>
       <c r="R43" t="n">
-        <v>6985249</v>
+        <v>6985513</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5118,10 +5111,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129431288</v>
+        <v>129431331</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5129,16 +5122,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5146,22 +5139,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>592108</v>
+        <v>592122</v>
       </c>
       <c r="R44" t="n">
-        <v>6985513</v>
+        <v>6985241</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5931,10 +5931,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129431287</v>
+        <v>129431321</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>56908</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5942,16 +5942,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5959,22 +5959,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>592138</v>
+        <v>592426</v>
       </c>
       <c r="R52" t="n">
-        <v>6985435</v>
+        <v>6985175</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6033,10 +6040,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129431321</v>
+        <v>129431287</v>
       </c>
       <c r="B53" t="n">
-        <v>56908</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6044,16 +6051,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6061,29 +6068,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>592426</v>
+        <v>592138</v>
       </c>
       <c r="R53" t="n">
-        <v>6985175</v>
+        <v>6985435</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>

--- a/artfynd/A 19278-2025 artfynd.xlsx
+++ b/artfynd/A 19278-2025 artfynd.xlsx
@@ -4484,10 +4484,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129431327</v>
+        <v>129431326</v>
       </c>
       <c r="B38" t="n">
-        <v>80149</v>
+        <v>57887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4495,34 +4495,46 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>592131</v>
+        <v>592165</v>
       </c>
       <c r="R38" t="n">
-        <v>6985450</v>
+        <v>6985420</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4581,10 +4593,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129431326</v>
+        <v>129431327</v>
       </c>
       <c r="B39" t="n">
-        <v>57887</v>
+        <v>80149</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4592,46 +4604,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>592165</v>
+        <v>592131</v>
       </c>
       <c r="R39" t="n">
-        <v>6985420</v>
+        <v>6985450</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5931,10 +5931,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129431321</v>
+        <v>129431287</v>
       </c>
       <c r="B52" t="n">
-        <v>56908</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5942,16 +5942,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5959,29 +5959,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>592426</v>
+        <v>592138</v>
       </c>
       <c r="R52" t="n">
-        <v>6985175</v>
+        <v>6985435</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6040,10 +6033,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129431287</v>
+        <v>129431321</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>56908</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6051,16 +6044,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6068,22 +6061,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>592138</v>
+        <v>592426</v>
       </c>
       <c r="R53" t="n">
-        <v>6985435</v>
+        <v>6985175</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>

--- a/artfynd/A 19278-2025 artfynd.xlsx
+++ b/artfynd/A 19278-2025 artfynd.xlsx
@@ -4484,10 +4484,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129431326</v>
+        <v>129431327</v>
       </c>
       <c r="B38" t="n">
-        <v>57887</v>
+        <v>80149</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4495,46 +4495,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>592165</v>
+        <v>592131</v>
       </c>
       <c r="R38" t="n">
-        <v>6985420</v>
+        <v>6985450</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4593,10 +4581,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129431327</v>
+        <v>129431326</v>
       </c>
       <c r="B39" t="n">
-        <v>80149</v>
+        <v>57887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4604,34 +4592,46 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>592131</v>
+        <v>592165</v>
       </c>
       <c r="R39" t="n">
-        <v>6985450</v>
+        <v>6985420</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4912,10 +4912,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129431332</v>
+        <v>129431331</v>
       </c>
       <c r="B42" t="n">
-        <v>80149</v>
+        <v>57724</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4923,34 +4923,46 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>592076</v>
+        <v>592122</v>
       </c>
       <c r="R42" t="n">
-        <v>6985249</v>
+        <v>6985241</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5009,10 +5021,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129431288</v>
+        <v>129431332</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5020,39 +5032,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>592108</v>
+        <v>592076</v>
       </c>
       <c r="R43" t="n">
-        <v>6985513</v>
+        <v>6985249</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5111,10 +5118,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129431331</v>
+        <v>129431288</v>
       </c>
       <c r="B44" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5122,16 +5129,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5139,29 +5146,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>592122</v>
+        <v>592108</v>
       </c>
       <c r="R44" t="n">
-        <v>6985241</v>
+        <v>6985513</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5931,10 +5931,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129431287</v>
+        <v>129431321</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>56908</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5942,16 +5942,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5959,22 +5959,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>592138</v>
+        <v>592426</v>
       </c>
       <c r="R52" t="n">
-        <v>6985435</v>
+        <v>6985175</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6033,10 +6040,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129431321</v>
+        <v>129431287</v>
       </c>
       <c r="B53" t="n">
-        <v>56908</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6044,16 +6051,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6061,29 +6068,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>592426</v>
+        <v>592138</v>
       </c>
       <c r="R53" t="n">
-        <v>6985175</v>
+        <v>6985435</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>

--- a/artfynd/A 19278-2025 artfynd.xlsx
+++ b/artfynd/A 19278-2025 artfynd.xlsx
@@ -4484,10 +4484,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129431327</v>
+        <v>129431326</v>
       </c>
       <c r="B38" t="n">
-        <v>80149</v>
+        <v>57887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4495,34 +4495,46 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>592131</v>
+        <v>592165</v>
       </c>
       <c r="R38" t="n">
-        <v>6985450</v>
+        <v>6985420</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4581,10 +4593,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129431326</v>
+        <v>129431327</v>
       </c>
       <c r="B39" t="n">
-        <v>57887</v>
+        <v>80149</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4592,46 +4604,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>592165</v>
+        <v>592131</v>
       </c>
       <c r="R39" t="n">
-        <v>6985420</v>
+        <v>6985450</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4690,10 +4690,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129431330</v>
+        <v>129431325</v>
       </c>
       <c r="B40" t="n">
-        <v>56920</v>
+        <v>57831</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4701,16 +4701,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102613</v>
+        <v>103031</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4720,15 +4720,11 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -4741,10 +4737,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>592177</v>
+        <v>592216</v>
       </c>
       <c r="R40" t="n">
-        <v>6985180</v>
+        <v>6985353</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4803,10 +4799,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129431325</v>
+        <v>129431330</v>
       </c>
       <c r="B41" t="n">
-        <v>57831</v>
+        <v>56920</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4814,16 +4810,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103031</v>
+        <v>102613</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4833,11 +4829,15 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>592216</v>
+        <v>592177</v>
       </c>
       <c r="R41" t="n">
-        <v>6985353</v>
+        <v>6985180</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5931,10 +5931,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129431321</v>
+        <v>129431287</v>
       </c>
       <c r="B52" t="n">
-        <v>56908</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5942,16 +5942,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5959,29 +5959,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>592426</v>
+        <v>592138</v>
       </c>
       <c r="R52" t="n">
-        <v>6985175</v>
+        <v>6985435</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6040,10 +6033,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129431287</v>
+        <v>129431321</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>56908</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6051,16 +6044,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6068,22 +6061,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>592138</v>
+        <v>592426</v>
       </c>
       <c r="R53" t="n">
-        <v>6985435</v>
+        <v>6985175</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>

--- a/artfynd/A 19278-2025 artfynd.xlsx
+++ b/artfynd/A 19278-2025 artfynd.xlsx
@@ -4168,10 +4168,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129431306</v>
+        <v>129431323</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>56908</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4179,16 +4179,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4196,12 +4196,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4211,10 +4215,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>592083</v>
+        <v>592351</v>
       </c>
       <c r="R35" t="n">
-        <v>6985107</v>
+        <v>6985215</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4241,12 +4245,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4273,10 +4277,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129431323</v>
+        <v>129431306</v>
       </c>
       <c r="B36" t="n">
-        <v>56908</v>
+        <v>57727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4284,16 +4288,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4301,16 +4305,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4320,10 +4320,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>592351</v>
+        <v>592083</v>
       </c>
       <c r="R36" t="n">
-        <v>6985215</v>
+        <v>6985107</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4484,10 +4484,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129431326</v>
+        <v>129431327</v>
       </c>
       <c r="B38" t="n">
-        <v>57887</v>
+        <v>80149</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4495,46 +4495,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>592165</v>
+        <v>592131</v>
       </c>
       <c r="R38" t="n">
-        <v>6985420</v>
+        <v>6985450</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4593,10 +4581,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129431327</v>
+        <v>129431326</v>
       </c>
       <c r="B39" t="n">
-        <v>80149</v>
+        <v>57887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4604,34 +4592,46 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>592131</v>
+        <v>592165</v>
       </c>
       <c r="R39" t="n">
-        <v>6985450</v>
+        <v>6985420</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5021,10 +5021,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129431332</v>
+        <v>129431288</v>
       </c>
       <c r="B43" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5032,34 +5032,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>592076</v>
+        <v>592108</v>
       </c>
       <c r="R43" t="n">
-        <v>6985249</v>
+        <v>6985513</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5118,10 +5123,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129431288</v>
+        <v>129431332</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5129,39 +5134,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>592108</v>
+        <v>592076</v>
       </c>
       <c r="R44" t="n">
-        <v>6985513</v>
+        <v>6985249</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>

--- a/artfynd/A 19278-2025 artfynd.xlsx
+++ b/artfynd/A 19278-2025 artfynd.xlsx
@@ -4168,10 +4168,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129431323</v>
+        <v>129431306</v>
       </c>
       <c r="B35" t="n">
-        <v>56908</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4179,16 +4179,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4196,16 +4196,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4215,10 +4211,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>592351</v>
+        <v>592083</v>
       </c>
       <c r="R35" t="n">
-        <v>6985215</v>
+        <v>6985107</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4245,12 +4241,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4277,10 +4273,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129431306</v>
+        <v>129431323</v>
       </c>
       <c r="B36" t="n">
-        <v>57727</v>
+        <v>56908</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4288,16 +4284,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4305,12 +4301,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -4320,10 +4320,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>592083</v>
+        <v>592351</v>
       </c>
       <c r="R36" t="n">
-        <v>6985107</v>
+        <v>6985215</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5021,10 +5021,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129431288</v>
+        <v>129431332</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5032,39 +5032,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>592108</v>
+        <v>592076</v>
       </c>
       <c r="R43" t="n">
-        <v>6985513</v>
+        <v>6985249</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5123,10 +5118,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129431332</v>
+        <v>129431288</v>
       </c>
       <c r="B44" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5134,34 +5129,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>592076</v>
+        <v>592108</v>
       </c>
       <c r="R44" t="n">
-        <v>6985249</v>
+        <v>6985513</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5931,10 +5931,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129431287</v>
+        <v>129431321</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>56908</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5942,16 +5942,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5959,22 +5959,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>592138</v>
+        <v>592426</v>
       </c>
       <c r="R52" t="n">
-        <v>6985435</v>
+        <v>6985175</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6033,10 +6040,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129431321</v>
+        <v>129431287</v>
       </c>
       <c r="B53" t="n">
-        <v>56908</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6044,16 +6051,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6061,29 +6068,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>592426</v>
+        <v>592138</v>
       </c>
       <c r="R53" t="n">
-        <v>6985175</v>
+        <v>6985435</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>

--- a/artfynd/A 19278-2025 artfynd.xlsx
+++ b/artfynd/A 19278-2025 artfynd.xlsx
@@ -4690,10 +4690,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129431325</v>
+        <v>129431330</v>
       </c>
       <c r="B40" t="n">
-        <v>57831</v>
+        <v>56920</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4701,16 +4701,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103031</v>
+        <v>102613</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4720,11 +4720,15 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -4737,10 +4741,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>592216</v>
+        <v>592177</v>
       </c>
       <c r="R40" t="n">
-        <v>6985353</v>
+        <v>6985180</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4799,10 +4803,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129431330</v>
+        <v>129431325</v>
       </c>
       <c r="B41" t="n">
-        <v>56920</v>
+        <v>57831</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4810,16 +4814,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102613</v>
+        <v>103031</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4829,15 +4833,11 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>592177</v>
+        <v>592216</v>
       </c>
       <c r="R41" t="n">
-        <v>6985180</v>
+        <v>6985353</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4912,10 +4912,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129431331</v>
+        <v>129431332</v>
       </c>
       <c r="B42" t="n">
-        <v>57724</v>
+        <v>80149</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4923,46 +4923,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>592122</v>
+        <v>592076</v>
       </c>
       <c r="R42" t="n">
-        <v>6985241</v>
+        <v>6985249</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5021,10 +5009,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129431332</v>
+        <v>129431331</v>
       </c>
       <c r="B43" t="n">
-        <v>80149</v>
+        <v>57724</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5032,34 +5020,46 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>592076</v>
+        <v>592122</v>
       </c>
       <c r="R43" t="n">
-        <v>6985249</v>
+        <v>6985241</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5220,7 +5220,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129431286</v>
+        <v>129431289</v>
       </c>
       <c r="B45" t="n">
         <v>57727</v>
@@ -5260,10 +5260,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>592152</v>
+        <v>592100</v>
       </c>
       <c r="R45" t="n">
-        <v>6985427</v>
+        <v>6985482</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5322,7 +5322,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129431289</v>
+        <v>129431286</v>
       </c>
       <c r="B46" t="n">
         <v>57727</v>
@@ -5362,10 +5362,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>592100</v>
+        <v>592152</v>
       </c>
       <c r="R46" t="n">
-        <v>6985482</v>
+        <v>6985427</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5931,10 +5931,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129431321</v>
+        <v>129431287</v>
       </c>
       <c r="B52" t="n">
-        <v>56908</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5942,16 +5942,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5959,29 +5959,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>592426</v>
+        <v>592138</v>
       </c>
       <c r="R52" t="n">
-        <v>6985175</v>
+        <v>6985435</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6040,10 +6033,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129431287</v>
+        <v>129431321</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>56908</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6051,16 +6044,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6068,22 +6061,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>592138</v>
+        <v>592426</v>
       </c>
       <c r="R53" t="n">
-        <v>6985435</v>
+        <v>6985175</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>

--- a/artfynd/A 19278-2025 artfynd.xlsx
+++ b/artfynd/A 19278-2025 artfynd.xlsx
@@ -3077,7 +3077,7 @@
         <v>129431324</v>
       </c>
       <c r="B24" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         <v>129431306</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4276,7 +4276,7 @@
         <v>129431323</v>
       </c>
       <c r="B36" t="n">
-        <v>56908</v>
+        <v>56911</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>129431285</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4487,7 +4487,7 @@
         <v>129431327</v>
       </c>
       <c r="B38" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4584,7 +4584,7 @@
         <v>129431326</v>
       </c>
       <c r="B39" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4690,10 +4690,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129431330</v>
+        <v>129431325</v>
       </c>
       <c r="B40" t="n">
-        <v>56920</v>
+        <v>57834</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4701,16 +4701,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102613</v>
+        <v>103031</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4720,15 +4720,11 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -4741,10 +4737,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>592177</v>
+        <v>592216</v>
       </c>
       <c r="R40" t="n">
-        <v>6985180</v>
+        <v>6985353</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4803,10 +4799,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129431325</v>
+        <v>129431330</v>
       </c>
       <c r="B41" t="n">
-        <v>57831</v>
+        <v>56923</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4814,16 +4810,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103031</v>
+        <v>102613</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4833,11 +4829,15 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
           <t>permanent revir</t>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>592216</v>
+        <v>592177</v>
       </c>
       <c r="R41" t="n">
-        <v>6985353</v>
+        <v>6985180</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4915,7 +4915,7 @@
         <v>129431332</v>
       </c>
       <c r="B42" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>129431331</v>
       </c>
       <c r="B43" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>129431288</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5220,10 +5220,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129431289</v>
+        <v>129431286</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5260,10 +5260,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>592100</v>
+        <v>592152</v>
       </c>
       <c r="R45" t="n">
-        <v>6985482</v>
+        <v>6985427</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5322,10 +5322,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129431286</v>
+        <v>129431289</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5362,10 +5362,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>592152</v>
+        <v>592100</v>
       </c>
       <c r="R46" t="n">
-        <v>6985427</v>
+        <v>6985482</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5427,7 +5427,7 @@
         <v>129431290</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>129431291</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>129431343</v>
       </c>
       <c r="B49" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>129431329</v>
       </c>
       <c r="B50" t="n">
-        <v>56908</v>
+        <v>56911</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>129431333</v>
       </c>
       <c r="B51" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>129431287</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         <v>129431321</v>
       </c>
       <c r="B53" t="n">
-        <v>56908</v>
+        <v>56911</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>129431342</v>
       </c>
       <c r="B54" t="n">
-        <v>80149</v>
+        <v>80175</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
